--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T19:34:42+00:00</t>
+    <t>2026-01-26T15:48:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T15:48:48+00:00</t>
+    <t>2026-01-28T08:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:09:20+00:00</t>
+    <t>2026-01-28T19:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation MedicationRequest Kategorie CodeSystem</t>
+    <t>ELGA e-Med MedicationRequest Kategorie CodeSystem</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:16:48+00:00</t>
+    <t>2026-01-29T15:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Zulässige Ausprägungen der MedicationRequest Kategorie. Dient der Unterscheidung von geplanten Abgaben und Medikationsplaneinträgen.</t>
+    <t>**Beschreibung:** Codesystem für zulässige Ausprägungen der MedicationRequest Kategorie. Dient der Unterscheidung von geplanten Abgaben und Medikationsplaneinträgen.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:27:43+00:00</t>
+    <t>2026-01-30T14:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Codesystem für zulässige Ausprägungen der MedicationRequest Kategorie. Dient der Unterscheidung von geplanten Abgaben und Medikationsplaneinträgen.</t>
+    <t>Codesystem für zulässige Ausprägungen der MedicationRequest Kategorie. Dient der Unterscheidung von geplanten Abgaben und Medikationsplaneinträgen.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -405,9 +405,7 @@
       <c r="A16" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>13</v>
-      </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:20:53+00:00</t>
+    <t>2026-05-11T15:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,7 +141,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Medikationsplaneintrag</t>
+    <t>Planeintrag</t>
   </si>
   <si>
     <t>Geplante Abgabe</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-main/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
